--- a/docs/content-import/toan-6-canh-dieu.xlsx
+++ b/docs/content-import/toan-6-canh-dieu.xlsx
@@ -7,6 +7,11 @@
     <sheet name="Blocks" sheetId="3" r:id="rId3"/>
     <sheet name="Flashcards" sheetId="4" r:id="rId4"/>
     <sheet name="Resources" sheetId="5" r:id="rId5"/>
+    <sheet name="QuestionBank" sheetId="6" r:id="rId6"/>
+    <sheet name="Questions" sheetId="7" r:id="rId7"/>
+    <sheet name="QuestionOptions" sheetId="8" r:id="rId8"/>
+    <sheet name="Exercises" sheetId="9" r:id="rId9"/>
+    <sheet name="ExerciseQuestions" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -122,6 +127,1662 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExerciseKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuestionKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-04</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-04</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-02</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-05</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-06</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-07</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-08</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-02</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-03</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-05</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-06</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-07</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-02</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-03</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-04</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-05</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-06</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-07</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-02</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-03</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-04</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-05</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-06</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-07</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-08</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-03</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-04</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-06</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-07</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-08</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-02</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-03</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-04</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-05</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-06</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-07</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-08</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-02</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-03</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-04</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-05</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-06</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-07</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-08</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-01</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-02</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-03</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-04</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-05</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-06</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-07</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-08</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-01</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-02</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-03</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-04</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-05</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-06</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-07</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-08</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
@@ -6887,4 +8548,5266 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BankKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BankName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngân hàng câu hỏi Toán 6 – Cánh Diều</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Câu hỏi trắc nghiệm / điền đáp số Toán 6 theo 6 chương của bộ Cánh Diều.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuestionKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BankKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NodeKey</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuestionType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Difficulty</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuestionText</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CorrectAnswer</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kết quả của phép tính 476 + 277 là:</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">753</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">476 + 277 = 753.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: 2367 &lt; 4416.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">So sánh: 2367 &lt; 4416.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trong số 67736, chữ số 6 ở hàng chục nghìn có giá trị bằng bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá trị = 6 × 10000 = 60000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá trị của luỹ thừa 3^4 là:</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3^4 = 3 × 3 × 3 × 3 = 81.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: 712 chia hết cho 2.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">712 : 2 là phép chia hết.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Số nào sau đây là số nguyên tố?</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 chỉ có hai ước là 1 và 2 nên là số nguyên tố.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phân tích số 36 ra thừa số nguyên tố (viết dạng tích luỹ thừa, ví dụ 2^2 × 3):</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2^2 × 3^2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36 = 2^2 × 3^2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá trị của ƯCLN(16, 7) là:</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ƯCLN(16, 7) = 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kết quả của phép tính (27) − (2) là:</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(27) − (2) = 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: -38 &gt; -40.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trên trục số, -38 nằm bên phải -40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá trị tuyệt đối |-17| bằng bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|-17| = 17 (khoảng cách từ điểm -17 đến gốc 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhiệt độ lúc đầu là -4°C, sau đó tăng 10°C. Nhiệt độ lúc sau là:</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6°C</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-4 + 10 = 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kết quả của phép tính (16) × (-4) là:</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-64</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(16) × (-4) = -64.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: -4 &gt; -10.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trên trục số, -4 nằm bên phải -10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá trị tuyệt đối |-15| bằng bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|-15| = 15 (khoảng cách từ điểm -15 đến gốc 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhiệt độ lúc đầu là 0°C, sau đó giảm 11°C. Nhiệt độ lúc sau là:</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-11°C</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 − 11 = -11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hình chữ nhật dài 13 cm, rộng 9 cm. Diện tích của nó là:</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117 cm²</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S = 13 × 9 = 117 (cm²).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: Hình lục giác đều có sáu cạnh bằng nhau.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đây là tính chất đúng của hình đó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chu vi hình chữ nhật dài 24 m, rộng 16 m bằng bao nhiêu mét?</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P = 2 × (24 + 16) = 80 (m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tam giác có đáy 32 cm, chiều cao 8 cm. Diện tích của tam giác là:</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128 cm²</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S = (đáy × chiều cao) : 2 = (32 × 8) : 2 = 128 (cm²).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Số trục đối xứng của hình chữ nhật (không phải hình vuông) là:</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hình chữ nhật (không phải hình vuông) có 2 trục đối xứng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: chữ in hoa "H" có trục đối xứng.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chữ H có ít nhất một trục đối xứng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-07</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: Hình chữ nhật có tâm đối xứng.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quay nửa vòng quanh tâm thì hình trùng chính nó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Số trục đối xứng của tam giác đều là bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tam giác đều có 3 trục đối xứng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gieo một con xúc xắc 35 lần thì có 14 lần xuất hiện mặt 6 chấm. Xác suất thực nghiệm của sự kiện "mặt 6 chấm" là bao nhiêu? (viết phân số tối giản)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xác suất thực nghiệm = 14/35 = 2/5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bảng số học sinh yêu thích 5 môn thể thao: 10; 2; 3; 6; 7. Tổng số học sinh được khảo sát là:</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cộng các giá trị: 10 + 2 + 3 + 6 + 7 = 28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: Khi tung đồng xu, khả năng ra mặt sấp và mặt ngửa là như nhau.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định đúng theo định nghĩa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bảng số học sinh đạt điểm giỏi: Toán: 14; Văn: 9; Anh: 11; Khoa học: 12; Thể dục: 8. Môn nào có nhiều học sinh đạt điểm giỏi nhất?</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toán</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá trị lớn nhất là 14 ứng với môn Toán.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gieo một con xúc xắc 33 lần thì có 4 lần xuất hiện mặt 6 chấm. Xác suất thực nghiệm của sự kiện "mặt 6 chấm" là bao nhiêu? (viết phân số tối giản)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/33</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xác suất thực nghiệm = 4/33 = 4/33.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bảng số học sinh yêu thích 5 môn thể thao: 2; 3; 7; 8; 8. Tổng số học sinh được khảo sát là:</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cộng các giá trị: 2 + 3 + 7 + 8 + 8 = 28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-07</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: Sự kiện ngẫu nhiên là sự kiện luôn xảy ra.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định này sai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bảng số học sinh đạt điểm giỏi: Toán: 14; Văn: 9; Anh: 13; Khoa học: 6; Thể dục: 6. Môn nào có nhiều học sinh đạt điểm giỏi nhất?</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toán</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giá trị lớn nhất là 14 ứng với môn Toán.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tính và rút gọn: 5/6 + 6/7 = ? (viết phân số tối giản dạng a/b)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71/42</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/6 + 6/7 = 71/42 = 71/42.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phân số nào lớn hơn: 1/8 hay 7/8?</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/8</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quy đồng: 1/8 = 8/64; 7/8 = 56/64.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kết quả của 4/7 × 2/4 (rút gọn) là:</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/7</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/7 × 2/4 = 8/28 = 2/7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: 2/6 = 6/19.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/6 ≠ 6/19 vì tích chéo khác nhau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-05</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kết quả của phép tính 18,6 + 2,4 là:</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18,6 + 2,4 = 21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Làm tròn số 59,80 đến hàng phần mười.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59,8</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhìn chữ số hàng phần trăm: 59,80 ≈ 59,8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50% của 115 là:</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57,5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115 × 50/100 = 57,5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: 7,64 &gt; 5,58.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">So sánh phần nguyên rồi phần thập phân: 7,64 &gt; 5,58.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc có số đo 169° là góc gì?</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc tù</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169° trong (90°; 180°) → góc tù.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cho đoạn thẳng AB = 34 cm, M là trung điểm của AB. Độ dài MA bằng bao nhiêu cm?</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MA = MB = AB : 2 = 34 : 2 = 17 (cm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: Trung điểm chia đoạn thẳng thành hai phần bằng nhau.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đây là tính chất hình học đúng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hai góc bù nhau, một góc có số đo 43°. Góc còn lại có số đo:</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137°</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tổng hai góc bù nhau bằng 180° nên góc còn lại = 180° − 43° = 137°.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-05</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc có số đo 122° là góc gì?</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc tù</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122° trong (90°; 180°) → góc tù.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-06</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FillBlank</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cho đoạn thẳng AB = 30 cm, M là trung điểm của AB. Độ dài MA bằng bao nhiêu cm?</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MA = MB = AB : 2 = 30 : 2 = 15 (cm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TrueFalse</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easy</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khẳng định sau đúng hay sai: Trung điểm chia đoạn thẳng thành hai phần bằng nhau.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đây là tính chất hình học đúng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MultipleChoice</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hai góc phụ nhau, một góc có số đo 60°. Góc còn lại có số đo:</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30°</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tổng hai góc phụ nhau bằng 90° nên góc còn lại = 90° − 60° = 30°.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QuestionKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OrderIndex</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OptionText</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IsCorrect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">745</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">758</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">753</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">747</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-08</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-08</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c1-08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7°C</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6°C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-14°C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-4°C</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-57</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-64</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-60</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-67</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-08</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-10°C</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-08</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11°C</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-08</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-11°C</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c2-08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0°C</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 cm²</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117 cm²</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130 cm²</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44 cm²</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256 cm²</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136 cm²</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40 cm²</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128 cm²</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-05</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-05</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-05</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c3-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-02</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-02</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-03</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-03</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khoa học</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toán</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anh</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-04</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thể dục</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-06</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-06</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-08</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anh</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-08</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Văn</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-08</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khoa học</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c4-08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toán</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-02</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bằng nhau</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/8</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-02</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1/8</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-03</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/28</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-03</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16/14</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-03</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2/7</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/11</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-04</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-04</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-05</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21,1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-05</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-05</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-05</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57,5</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107,5</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58,5</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-08</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c5-08</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-01</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc vuông</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-01</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc bẹt</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-01</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc nhọn</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-01</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc tù</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-03</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-03</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-04</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137°</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-04</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180°</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-04</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147°</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-04</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">43°</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-05</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc vuông</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-05</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc nhọn</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-05</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc tù</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-05</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Góc bẹt</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-07</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đúng</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sai</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-08</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30°</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-08</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90°</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-08</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60°</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-c6-08</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40°</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExerciseKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NodeKey</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExerciseName</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ExerciseType</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tier</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DurationMinutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaxAttempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PassingPercent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-lt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luyện tập — Số tự nhiên</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Practice</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c1-kt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đề kiểm tra — Số tự nhiên</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-lt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luyện tập — Số nguyên</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Practice</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c2-kt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đề kiểm tra — Số nguyên</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-lt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luyện tập — Hình học trực quan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Practice</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c3-kt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đề kiểm tra — Hình học trực quan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-lt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luyện tập — Một số yếu tố thống kê và xác suất</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Practice</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c4-kt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đề kiểm tra — Một số yếu tố thống kê và xác suất</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-lt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luyện tập — Phân số và số thập phân</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Practice</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c5-kt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đề kiểm tra — Phân số và số thập phân</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-lt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luyện tập — Hình học phẳng</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Practice</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cd6-ex-c6-kt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đề kiểm tra — Hình học phẳng</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standard</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>